--- a/Excel/EquipReformFeeConfig.xlsx
+++ b/Excel/EquipReformFeeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1032,7 +1037,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XER26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1043,7 +1048,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8 16371:16372">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1053,7 +1058,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8 16371:16372">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1063,7 +1068,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1085,7 +1090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1107,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:8 16371:16372">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
@@ -1129,7 +1134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="6" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1153,21 +1158,21 @@
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="7" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D18" si="0">E6+1</f>
+        <f t="shared" ref="D7:D19" si="0">E6+1</f>
         <v>51</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F18" si="1">F6+G6*(E6-D6)</f>
+        <f t="shared" ref="F7:F19" si="1">F6+G6*(E6-D6)</f>
         <v>2550</v>
       </c>
       <c r="G7" s="7">
@@ -1179,7 +1184,7 @@
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="8" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1205,7 +1210,7 @@
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="9" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1231,7 +1236,7 @@
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="10" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1257,7 +1262,7 @@
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="11" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1283,7 +1288,7 @@
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="12" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -1309,7 +1314,7 @@
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="13" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -1335,7 +1340,7 @@
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="14" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -1361,7 +1366,7 @@
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="15" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
@@ -1387,7 +1392,7 @@
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="16" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -1413,7 +1418,7 @@
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="17" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2">
@@ -1439,7 +1444,7 @@
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="18" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
@@ -1465,19 +1470,33 @@
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="19" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>1501</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2000</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="1"/>
+        <v>8428300</v>
+      </c>
+      <c r="G19" s="7">
+        <v>25000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>80</v>
+      </c>
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="20" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1489,7 +1508,7 @@
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="21" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1501,7 +1520,7 @@
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="22" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1513,7 +1532,7 @@
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="23" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1525,7 +1544,7 @@
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="24" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1537,7 +1556,7 @@
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="25" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1549,7 +1568,7 @@
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" ht="14" spans="1:8 16371:16372">
+    <row r="26" customFormat="1" customHeight="1" spans="1:8 16371:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
